--- a/Impfquoten/Impfquoten-13.04.2021.xlsx
+++ b/Impfquoten/Impfquoten-13.04.2021.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Projekte\Abt3_IQM-COVID19\Fachlich\Auswertungen\2021-04-14\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B869908-89D2-432C-815E-1F49F7D4D994}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51CDBC37-2E19-4CCF-A5CD-0FBFC9FC249F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="105" windowWidth="28515" windowHeight="12600" tabRatio="825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="120" yWindow="105" windowWidth="28515" windowHeight="12600" tabRatio="825" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Erläuterung" sheetId="9" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="81">
   <si>
     <t>Bayern</t>
   </si>
@@ -199,9 +199,6 @@
     <t>* Impfungen, die in den bundeseigenen Impfzentren aus dem Impfkontingent des Bundes durchgeführt wurden. Dies sind Impfungen, die Angehörigen des Bundes gemäß §§ 2, 3 und 4 Coronavirus-Impfverordnung verabreicht wurden. Eine Impfquote kann aufgrund einer fehlenden Nennerpopulation nich berechnet werden, die Impfungen gehen allerdings in die Berechnung der Impfquote für Gesamtdeutschland mit ein.</t>
   </si>
   <si>
-    <t>* Impfungen, die in den bundeseigenen Impfzentren aus dem Impfkontingent des Bundes durchgeführt wurden. Dies sind Impfungen, die Angehörigen des Bundes gemäß §§ 2, 3 und 4 Coronavirus-Impfverordnung verabreicht wurden. Die Impfungen gehen in die Gesamtzahl der Impfungen für Gesamtdeutschland mit ein.</t>
-  </si>
-  <si>
     <t>Gesamtzahl  einmalig geimpft</t>
   </si>
   <si>
@@ -263,6 +260,18 @@
   </si>
   <si>
     <t>In den Gesamtsummen der Zweitimpfung und der täglichen Gesamtzahlen sind n=2.083 Impfungen enthalten, die entsprechend den vorliegenden Meldedaten nicht plausibel einem Impfdatum zugewiesen werden können.</t>
+  </si>
+  <si>
+    <t>Hessen*</t>
+  </si>
+  <si>
+    <t>Impfzentren Bund**</t>
+  </si>
+  <si>
+    <t>** Impfungen, die in den bundeseigenen Impfzentren aus dem Impfkontingent des Bundes durchgeführt wurden. Dies sind Impfungen, die Angehörigen des Bundes gemäß §§ 2, 3 und 4 Coronavirus-Impfverordnung verabreicht wurden. Die Impfungen gehen in die Gesamtzahl der Impfungen für Gesamtdeutschland mit ein.</t>
+  </si>
+  <si>
+    <t>* Aus Hessen konnten aufgrund eines Softwarefehlers keine Daten der Impfzentren, Mobilen Teams und Krankenhäuser für den Impftag 13.4.2021 gemeldet werden.</t>
   </si>
 </sst>
 </file>
@@ -702,6 +711,33 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -719,15 +755,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -756,24 +783,6 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Komma 2" xfId="4" xr:uid="{B797BBD4-588A-432F-99CA-840AA723A419}"/>
@@ -1135,7 +1144,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="2"/>
@@ -1147,12 +1156,12 @@
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1170,7 +1179,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1197,22 +1206,22 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="58" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
@@ -1259,102 +1268,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="62" t="s">
+      <c r="C1" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62" t="s">
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q1" s="73"/>
+      <c r="R1" s="73"/>
+      <c r="S1" s="73"/>
     </row>
     <row r="2" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="60"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="63" t="s">
+      <c r="A2" s="71"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D2" s="70" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="70" t="s">
         <v>57</v>
       </c>
-      <c r="E2" s="59" t="s">
-        <v>58</v>
-      </c>
-      <c r="F2" s="63" t="s">
+      <c r="F2" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63" t="s">
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="J2" s="63"/>
-      <c r="K2" s="63"/>
-      <c r="L2" s="64" t="s">
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="M2" s="64"/>
-      <c r="N2" s="64" t="s">
+      <c r="M2" s="75"/>
+      <c r="N2" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="O2" s="64"/>
-      <c r="P2" s="64" t="s">
+      <c r="O2" s="75"/>
+      <c r="P2" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="Q2" s="64"/>
-      <c r="R2" s="64" t="s">
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="S2" s="64"/>
+      <c r="S2" s="75"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A3" s="60"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="64"/>
-      <c r="O3" s="64"/>
-      <c r="P3" s="64"/>
-      <c r="Q3" s="64"/>
-      <c r="R3" s="64"/>
-      <c r="S3" s="64"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="74"/>
+      <c r="K3" s="74"/>
+      <c r="L3" s="75"/>
+      <c r="M3" s="75"/>
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="61"/>
-      <c r="B4" s="61"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
       <c r="F4" s="14" t="s">
         <v>19</v>
       </c>
@@ -1477,31 +1486,31 @@
         <v>17.0829099280237</v>
       </c>
       <c r="G6" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I6" s="24">
         <v>6.6122772593462251</v>
       </c>
       <c r="J6" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K6" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L6" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M6" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N6" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O6" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P6" s="27">
         <v>54259</v>
@@ -1536,31 +1545,31 @@
         <v>17.088092054184081</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H7" s="33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I7" s="32">
         <v>7.4526412518793483</v>
       </c>
       <c r="J7" s="33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K7" s="33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L7" s="34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M7" s="34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N7" s="34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O7" s="34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P7" s="35">
         <v>25927</v>
@@ -1595,31 +1604,31 @@
         <v>17.021023493066519</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H8" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I8" s="24">
         <v>5.7347397371736237</v>
       </c>
       <c r="J8" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K8" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L8" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M8" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N8" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O8" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P8" s="27">
         <v>14699</v>
@@ -1772,31 +1781,31 @@
         <v>15.173948168598365</v>
       </c>
       <c r="G11" s="33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H11" s="33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I11" s="32">
         <v>6.6421069706492277</v>
       </c>
       <c r="J11" s="33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K11" s="33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L11" s="34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M11" s="34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N11" s="34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O11" s="34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P11" s="35">
         <v>25345</v>
@@ -2126,31 +2135,31 @@
         <v>16.471531845388878</v>
       </c>
       <c r="G17" s="33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H17" s="33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I17" s="32">
         <v>7.0363222134931709</v>
       </c>
       <c r="J17" s="33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K17" s="33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L17" s="34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M17" s="34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N17" s="34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O17" s="34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P17" s="35">
         <v>13037</v>
@@ -2185,31 +2194,31 @@
         <v>17.71579136333358</v>
       </c>
       <c r="G18" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H18" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I18" s="24">
         <v>5.4258691751618153</v>
       </c>
       <c r="J18" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K18" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L18" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M18" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N18" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O18" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P18" s="27">
         <v>6902</v>
@@ -2303,31 +2312,31 @@
         <v>17.484524542767385</v>
       </c>
       <c r="G20" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H20" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I20" s="24">
         <v>7.4560157646699263</v>
       </c>
       <c r="J20" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K20" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L20" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M20" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N20" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O20" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P20" s="28">
         <v>5315</v>
@@ -2357,22 +2366,22 @@
         <v>52</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G21" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H21" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I21" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J21" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K21" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L21" s="35">
         <v>26519</v>
@@ -2387,16 +2396,16 @@
         <v>1</v>
       </c>
       <c r="P21" s="35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q21" s="35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R21" s="35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S21" s="35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2417,31 +2426,31 @@
         <v>16.903793393969853</v>
       </c>
       <c r="G22" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H22" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I22" s="41">
         <v>6.2358303432247064</v>
       </c>
       <c r="J22" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K22" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L22" s="43" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M22" s="43" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N22" s="43" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O22" s="43" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P22" s="52">
         <v>342667</v>
@@ -2458,135 +2467,130 @@
     </row>
     <row r="23" spans="1:20" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" s="65" t="s">
+      <c r="A25" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="65"/>
-      <c r="C25" s="65"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="65"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="65"/>
-      <c r="H25" s="65"/>
-      <c r="I25" s="65"/>
-      <c r="J25" s="65"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="65"/>
-      <c r="M25" s="65"/>
-      <c r="N25" s="65"/>
-      <c r="O25" s="65"/>
-      <c r="P25" s="65"/>
-      <c r="Q25" s="65"/>
-      <c r="R25" s="65"/>
-      <c r="S25" s="65"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="67"/>
+      <c r="G25" s="67"/>
+      <c r="H25" s="67"/>
+      <c r="I25" s="67"/>
+      <c r="J25" s="67"/>
+      <c r="K25" s="67"/>
+      <c r="L25" s="67"/>
+      <c r="M25" s="67"/>
+      <c r="N25" s="67"/>
+      <c r="O25" s="67"/>
+      <c r="P25" s="67"/>
+      <c r="Q25" s="67"/>
+      <c r="R25" s="67"/>
+      <c r="S25" s="67"/>
       <c r="T25" s="54"/>
     </row>
     <row r="26" spans="1:20" s="7" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="67" t="s">
+      <c r="A26" s="69" t="s">
+        <v>63</v>
+      </c>
+      <c r="B26" s="69"/>
+      <c r="C26" s="69"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="69"/>
+      <c r="F26" s="69"/>
+      <c r="G26" s="69"/>
+      <c r="H26" s="69"/>
+      <c r="I26" s="69"/>
+      <c r="J26" s="69"/>
+      <c r="K26" s="69"/>
+      <c r="L26" s="69"/>
+      <c r="M26" s="69"/>
+      <c r="N26" s="69"/>
+      <c r="O26" s="69"/>
+      <c r="P26" s="69"/>
+      <c r="Q26" s="69"/>
+      <c r="R26" s="69"/>
+      <c r="S26" s="69"/>
+      <c r="T26" s="55"/>
+    </row>
+    <row r="27" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="67"/>
-      <c r="C26" s="67"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
-      <c r="F26" s="67"/>
-      <c r="G26" s="67"/>
-      <c r="H26" s="67"/>
-      <c r="I26" s="67"/>
-      <c r="J26" s="67"/>
-      <c r="K26" s="67"/>
-      <c r="L26" s="67"/>
-      <c r="M26" s="67"/>
-      <c r="N26" s="67"/>
-      <c r="O26" s="67"/>
-      <c r="P26" s="67"/>
-      <c r="Q26" s="67"/>
-      <c r="R26" s="67"/>
-      <c r="S26" s="67"/>
-      <c r="T26" s="55"/>
-    </row>
-    <row r="27" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="66" t="s">
+      <c r="B27" s="68"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="68"/>
+      <c r="K27" s="68"/>
+      <c r="L27" s="68"/>
+      <c r="M27" s="68"/>
+      <c r="N27" s="68"/>
+      <c r="O27" s="68"/>
+      <c r="P27" s="68"/>
+      <c r="Q27" s="68"/>
+      <c r="R27" s="68"/>
+      <c r="S27" s="68"/>
+      <c r="T27" s="68"/>
+    </row>
+    <row r="28" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="66"/>
-      <c r="C27" s="66"/>
-      <c r="D27" s="66"/>
-      <c r="E27" s="66"/>
-      <c r="F27" s="66"/>
-      <c r="G27" s="66"/>
-      <c r="H27" s="66"/>
-      <c r="I27" s="66"/>
-      <c r="J27" s="66"/>
-      <c r="K27" s="66"/>
-      <c r="L27" s="66"/>
-      <c r="M27" s="66"/>
-      <c r="N27" s="66"/>
-      <c r="O27" s="66"/>
-      <c r="P27" s="66"/>
-      <c r="Q27" s="66"/>
-      <c r="R27" s="66"/>
-      <c r="S27" s="66"/>
-      <c r="T27" s="66"/>
-    </row>
-    <row r="28" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="B28" s="66"/>
-      <c r="C28" s="66"/>
-      <c r="D28" s="66"/>
-      <c r="E28" s="66"/>
-      <c r="F28" s="66"/>
-      <c r="G28" s="66"/>
-      <c r="H28" s="66"/>
-      <c r="I28" s="66"/>
-      <c r="J28" s="66"/>
-      <c r="K28" s="66"/>
-      <c r="L28" s="66"/>
-      <c r="M28" s="66"/>
-      <c r="N28" s="66"/>
-      <c r="O28" s="66"/>
-      <c r="P28" s="66"/>
-      <c r="Q28" s="66"/>
-      <c r="R28" s="66"/>
-      <c r="S28" s="66"/>
-      <c r="T28" s="66"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="68"/>
+      <c r="H28" s="68"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="68"/>
+      <c r="L28" s="68"/>
+      <c r="M28" s="68"/>
+      <c r="N28" s="68"/>
+      <c r="O28" s="68"/>
+      <c r="P28" s="68"/>
+      <c r="Q28" s="68"/>
+      <c r="R28" s="68"/>
+      <c r="S28" s="68"/>
+      <c r="T28" s="68"/>
     </row>
     <row r="29" spans="1:20" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="67" t="s">
+      <c r="A29" s="69" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="67"/>
-      <c r="C29" s="67"/>
-      <c r="D29" s="67"/>
-      <c r="E29" s="67"/>
-      <c r="F29" s="67"/>
-      <c r="G29" s="67"/>
-      <c r="H29" s="67"/>
-      <c r="I29" s="67"/>
-      <c r="J29" s="67"/>
-      <c r="K29" s="67"/>
-      <c r="L29" s="67"/>
-      <c r="M29" s="67"/>
-      <c r="N29" s="67"/>
-      <c r="O29" s="67"/>
-      <c r="P29" s="67"/>
-      <c r="Q29" s="67"/>
-      <c r="R29" s="67"/>
-      <c r="S29" s="67"/>
-      <c r="T29" s="67"/>
+      <c r="B29" s="69"/>
+      <c r="C29" s="69"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="69"/>
+      <c r="G29" s="69"/>
+      <c r="H29" s="69"/>
+      <c r="I29" s="69"/>
+      <c r="J29" s="69"/>
+      <c r="K29" s="69"/>
+      <c r="L29" s="69"/>
+      <c r="M29" s="69"/>
+      <c r="N29" s="69"/>
+      <c r="O29" s="69"/>
+      <c r="P29" s="69"/>
+      <c r="Q29" s="69"/>
+      <c r="R29" s="69"/>
+      <c r="S29" s="69"/>
+      <c r="T29" s="69"/>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A25:S25"/>
-    <mergeCell ref="A27:T27"/>
-    <mergeCell ref="A29:T29"/>
-    <mergeCell ref="A28:T28"/>
-    <mergeCell ref="A26:S26"/>
     <mergeCell ref="A1:A4"/>
     <mergeCell ref="B1:B4"/>
     <mergeCell ref="C1:K1"/>
@@ -2601,6 +2605,11 @@
     <mergeCell ref="R2:S3"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="E2:E4"/>
+    <mergeCell ref="A25:S25"/>
+    <mergeCell ref="A27:T27"/>
+    <mergeCell ref="A29:T29"/>
+    <mergeCell ref="A28:T28"/>
+    <mergeCell ref="A26:S26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2609,7 +2618,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87F4549C-7AD6-45E3-9E9E-50890FFA92FE}">
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:V28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.28515625" style="3" customWidth="1"/>
@@ -2624,112 +2633,112 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="79" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="76" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="69"/>
-      <c r="H1" s="69"/>
-      <c r="I1" s="69"/>
-      <c r="J1" s="69"/>
-      <c r="K1" s="69"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="68" t="s">
-        <v>63</v>
-      </c>
-      <c r="N1" s="69"/>
-      <c r="O1" s="69"/>
-      <c r="P1" s="69"/>
-      <c r="Q1" s="69"/>
-      <c r="R1" s="69"/>
-      <c r="S1" s="69"/>
-      <c r="T1" s="69"/>
-      <c r="U1" s="69"/>
-      <c r="V1" s="70"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="76" t="s">
+        <v>62</v>
+      </c>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="77"/>
+      <c r="Q1" s="77"/>
+      <c r="R1" s="77"/>
+      <c r="S1" s="77"/>
+      <c r="T1" s="77"/>
+      <c r="U1" s="77"/>
+      <c r="V1" s="78"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="72"/>
-      <c r="B2" s="75"/>
-      <c r="C2" s="62" t="s">
+      <c r="A2" s="80"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="73" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="68" t="s">
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="76" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="62" t="s">
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="73" t="s">
         <v>51</v>
       </c>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="68" t="s">
+      <c r="N2" s="73"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="76" t="s">
         <v>52</v>
       </c>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
-      <c r="U2" s="69"/>
-      <c r="V2" s="70"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="78"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="72"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="62" t="s">
+      <c r="A3" s="80"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62" t="s">
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="68" t="s">
+      <c r="H3" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="69"/>
-      <c r="J3" s="69"/>
-      <c r="K3" s="70"/>
-      <c r="L3" s="62" t="s">
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="78"/>
+      <c r="L3" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="M3" s="62" t="s">
+      <c r="M3" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="62"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="62"/>
-      <c r="Q3" s="62" t="s">
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="R3" s="68" t="s">
+      <c r="R3" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="S3" s="69"/>
-      <c r="T3" s="69"/>
-      <c r="U3" s="70"/>
-      <c r="V3" s="62" t="s">
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="73" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="73"/>
-      <c r="B4" s="76"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="84"/>
       <c r="C4" s="14" t="s">
         <v>19</v>
       </c>
@@ -2742,7 +2751,7 @@
       <c r="F4" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="62"/>
+      <c r="G4" s="73"/>
       <c r="H4" s="14" t="s">
         <v>19</v>
       </c>
@@ -2755,7 +2764,7 @@
       <c r="K4" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="L4" s="62"/>
+      <c r="L4" s="73"/>
       <c r="M4" s="14" t="s">
         <v>19</v>
       </c>
@@ -2768,7 +2777,7 @@
       <c r="P4" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="Q4" s="62"/>
+      <c r="Q4" s="73"/>
       <c r="R4" s="14" t="s">
         <v>19</v>
       </c>
@@ -2781,7 +2790,7 @@
       <c r="U4" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="V4" s="62"/>
+      <c r="V4" s="73"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
@@ -3196,7 +3205,7 @@
         <v>29</v>
       </c>
       <c r="B11" s="44" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="C11" s="45">
         <v>871910</v>
@@ -3874,7 +3883,7 @@
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="29"/>
       <c r="B21" s="44" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="C21" s="45">
         <v>28309</v>
@@ -3907,34 +3916,34 @@
         <v>0</v>
       </c>
       <c r="M21" s="50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N21" s="50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O21" s="50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P21" s="50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q21" s="50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R21" s="50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S21" s="50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T21" s="50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U21" s="50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="V21" s="50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4011,37 +4020,50 @@
     </row>
     <row r="26" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="67" t="s">
-        <v>56</v>
-      </c>
-      <c r="C27" s="67"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="67"/>
-      <c r="F27" s="67"/>
-      <c r="G27" s="67"/>
-      <c r="H27" s="67"/>
-      <c r="I27" s="67"/>
-      <c r="J27" s="67"/>
-      <c r="K27" s="67"/>
-      <c r="L27" s="67"/>
-      <c r="M27" s="67"/>
-      <c r="N27" s="67"/>
-      <c r="O27" s="67"/>
-      <c r="P27" s="67"/>
-      <c r="Q27" s="67"/>
-      <c r="R27" s="67"/>
-      <c r="S27" s="67"/>
-      <c r="T27" s="67"/>
-      <c r="U27" s="67"/>
-      <c r="V27" s="67"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B27" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="69" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="69"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="69"/>
+      <c r="H28" s="69"/>
+      <c r="I28" s="69"/>
+      <c r="J28" s="69"/>
+      <c r="K28" s="69"/>
+      <c r="L28" s="69"/>
+      <c r="M28" s="69"/>
+      <c r="N28" s="69"/>
+      <c r="O28" s="69"/>
+      <c r="P28" s="69"/>
+      <c r="Q28" s="69"/>
+      <c r="R28" s="69"/>
+      <c r="S28" s="69"/>
+      <c r="T28" s="69"/>
+      <c r="U28" s="69"/>
+      <c r="V28" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B27:V27"/>
+    <mergeCell ref="M1:V1"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="B28:V28"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="M2:Q2"/>
@@ -4050,14 +4072,6 @@
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="R3:U3"/>
     <mergeCell ref="V3:V4"/>
-    <mergeCell ref="M1:V1"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="C1:L1"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="L3:L4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId1"/>
@@ -4075,1539 +4089,1539 @@
     <col min="5" max="16384" width="11.42578125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="75" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+    <row r="1" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="59" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="78" t="s">
+      <c r="C1" s="60" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="78" t="s">
+      <c r="D1" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="79" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="62">
+        <v>44192</v>
+      </c>
+      <c r="B2" s="63">
+        <v>24159</v>
+      </c>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63">
+        <v>24159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="62">
+        <v>44193</v>
+      </c>
+      <c r="B3" s="63">
+        <v>18383</v>
+      </c>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63">
+        <v>18383</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="62">
+        <v>44194</v>
+      </c>
+      <c r="B4" s="63">
+        <v>48305</v>
+      </c>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63">
+        <v>48305</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="62">
+        <v>44195</v>
+      </c>
+      <c r="B5" s="63">
+        <v>61542</v>
+      </c>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63">
+        <v>61542</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="62">
+        <v>44196</v>
+      </c>
+      <c r="B6" s="63">
+        <v>49555</v>
+      </c>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63">
+        <v>49555</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="62">
+        <v>44197</v>
+      </c>
+      <c r="B7" s="63">
+        <v>19271</v>
+      </c>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63">
+        <v>19271</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="62">
+        <v>44198</v>
+      </c>
+      <c r="B8" s="63">
+        <v>52442</v>
+      </c>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63">
+        <v>52442</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="62">
+        <v>44199</v>
+      </c>
+      <c r="B9" s="63">
+        <v>24148</v>
+      </c>
+      <c r="C9" s="63"/>
+      <c r="D9" s="63">
+        <v>24148</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="62">
+        <v>44200</v>
+      </c>
+      <c r="B10" s="63">
+        <v>48306</v>
+      </c>
+      <c r="C10" s="63"/>
+      <c r="D10" s="63">
+        <v>48306</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="62">
+        <v>44201</v>
+      </c>
+      <c r="B11" s="63">
+        <v>53341</v>
+      </c>
+      <c r="C11" s="63"/>
+      <c r="D11" s="63">
+        <v>53341</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="62">
+        <v>44202</v>
+      </c>
+      <c r="B12" s="63">
+        <v>62995</v>
+      </c>
+      <c r="C12" s="63"/>
+      <c r="D12" s="63">
+        <v>62995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="62">
+        <v>44203</v>
+      </c>
+      <c r="B13" s="63">
+        <v>56201</v>
+      </c>
+      <c r="C13" s="63"/>
+      <c r="D13" s="63">
+        <v>56201</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="62">
+        <v>44204</v>
+      </c>
+      <c r="B14" s="63">
+        <v>63101</v>
+      </c>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63">
+        <v>63101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="62">
+        <v>44205</v>
+      </c>
+      <c r="B15" s="63">
+        <v>61176</v>
+      </c>
+      <c r="C15" s="63"/>
+      <c r="D15" s="63">
+        <v>61176</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="62">
+        <v>44206</v>
+      </c>
+      <c r="B16" s="63">
+        <v>35132</v>
+      </c>
+      <c r="C16" s="63"/>
+      <c r="D16" s="63">
+        <v>35132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="62">
+        <v>44207</v>
+      </c>
+      <c r="B17" s="63">
+        <v>66389</v>
+      </c>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63">
+        <v>66389</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="62">
+        <v>44208</v>
+      </c>
+      <c r="B18" s="63">
+        <v>82874</v>
+      </c>
+      <c r="C18" s="63"/>
+      <c r="D18" s="63">
+        <v>82874</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="62">
+        <v>44209</v>
+      </c>
+      <c r="B19" s="63">
+        <v>111147</v>
+      </c>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63">
+        <v>111147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="62">
+        <v>44210</v>
+      </c>
+      <c r="B20" s="63">
+        <v>82836</v>
+      </c>
+      <c r="C20" s="63"/>
+      <c r="D20" s="63">
+        <v>82836</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="62">
+        <v>44211</v>
+      </c>
+      <c r="B21" s="63">
+        <v>89715</v>
+      </c>
+      <c r="C21" s="63">
+        <v>712</v>
+      </c>
+      <c r="D21" s="63">
+        <v>90427</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="62">
+        <v>44212</v>
+      </c>
+      <c r="B22" s="63">
+        <v>56317</v>
+      </c>
+      <c r="C22" s="63">
+        <v>1036</v>
+      </c>
+      <c r="D22" s="63">
+        <v>57353</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="62">
+        <v>44213</v>
+      </c>
+      <c r="B23" s="63">
+        <v>30827</v>
+      </c>
+      <c r="C23" s="63">
+        <v>16667</v>
+      </c>
+      <c r="D23" s="63">
+        <v>47494</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="62">
+        <v>44214</v>
+      </c>
+      <c r="B24" s="63">
+        <v>66053</v>
+      </c>
+      <c r="C24" s="63">
+        <v>15745</v>
+      </c>
+      <c r="D24" s="63">
+        <v>81798</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="62">
+        <v>44215</v>
+      </c>
+      <c r="B25" s="63">
+        <v>81041</v>
+      </c>
+      <c r="C25" s="63">
+        <v>32452</v>
+      </c>
+      <c r="D25" s="63">
+        <v>113493</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="62">
+        <v>44216</v>
+      </c>
+      <c r="B26" s="63">
+        <v>80333</v>
+      </c>
+      <c r="C26" s="63">
+        <v>51055</v>
+      </c>
+      <c r="D26" s="63">
+        <v>131388</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="62">
+        <v>44217</v>
+      </c>
+      <c r="B27" s="63">
+        <v>64349</v>
+      </c>
+      <c r="C27" s="63">
+        <v>39674</v>
+      </c>
+      <c r="D27" s="63">
+        <v>104023</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="62">
+        <v>44218</v>
+      </c>
+      <c r="B28" s="63">
+        <v>67515</v>
+      </c>
+      <c r="C28" s="63">
+        <v>34378</v>
+      </c>
+      <c r="D28" s="63">
+        <v>101893</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="62">
+        <v>44219</v>
+      </c>
+      <c r="B29" s="63">
+        <v>40686</v>
+      </c>
+      <c r="C29" s="63">
+        <v>44677</v>
+      </c>
+      <c r="D29" s="63">
+        <v>85363</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="62">
+        <v>44220</v>
+      </c>
+      <c r="B30" s="63">
+        <v>25596</v>
+      </c>
+      <c r="C30" s="63">
+        <v>23897</v>
+      </c>
+      <c r="D30" s="63">
+        <v>49493</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="62">
+        <v>44221</v>
+      </c>
+      <c r="B31" s="63">
+        <v>58179</v>
+      </c>
+      <c r="C31" s="63">
+        <v>37792</v>
+      </c>
+      <c r="D31" s="63">
+        <v>95971</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="62">
+        <v>44222</v>
+      </c>
+      <c r="B32" s="63">
+        <v>50966</v>
+      </c>
+      <c r="C32" s="63">
+        <v>48453</v>
+      </c>
+      <c r="D32" s="63">
+        <v>99419</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="62">
+        <v>44223</v>
+      </c>
+      <c r="B33" s="63">
+        <v>51577</v>
+      </c>
+      <c r="C33" s="63">
+        <v>59331</v>
+      </c>
+      <c r="D33" s="63">
+        <v>110908</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="62">
+        <v>44224</v>
+      </c>
+      <c r="B34" s="63">
+        <v>45185</v>
+      </c>
+      <c r="C34" s="63">
+        <v>46146</v>
+      </c>
+      <c r="D34" s="63">
+        <v>91331</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="62">
+        <v>44225</v>
+      </c>
+      <c r="B35" s="63">
+        <v>51179</v>
+      </c>
+      <c r="C35" s="63">
+        <v>57339</v>
+      </c>
+      <c r="D35" s="63">
+        <v>108518</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="62">
+        <v>44226</v>
+      </c>
+      <c r="B36" s="63">
+        <v>35290</v>
+      </c>
+      <c r="C36" s="63">
+        <v>51306</v>
+      </c>
+      <c r="D36" s="63">
+        <v>86596</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="62">
+        <v>44227</v>
+      </c>
+      <c r="B37" s="63">
+        <v>26718</v>
+      </c>
+      <c r="C37" s="63">
+        <v>31051</v>
+      </c>
+      <c r="D37" s="63">
+        <v>57769</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="62">
+        <v>44228</v>
+      </c>
+      <c r="B38" s="63">
+        <v>59267</v>
+      </c>
+      <c r="C38" s="63">
+        <v>62136</v>
+      </c>
+      <c r="D38" s="63">
+        <v>121403</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="62">
+        <v>44229</v>
+      </c>
+      <c r="B39" s="63">
+        <v>63543</v>
+      </c>
+      <c r="C39" s="63">
+        <v>66948</v>
+      </c>
+      <c r="D39" s="63">
+        <v>130491</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="62">
+        <v>44230</v>
+      </c>
+      <c r="B40" s="63">
+        <v>63689</v>
+      </c>
+      <c r="C40" s="63">
+        <v>94243</v>
+      </c>
+      <c r="D40" s="63">
+        <v>157932</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="62">
+        <v>44231</v>
+      </c>
+      <c r="B41" s="63">
+        <v>61020</v>
+      </c>
+      <c r="C41" s="63">
+        <v>70133</v>
+      </c>
+      <c r="D41" s="63">
+        <v>131153</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="62">
+        <v>44232</v>
+      </c>
+      <c r="B42" s="63">
+        <v>66405</v>
+      </c>
+      <c r="C42" s="63">
+        <v>76620</v>
+      </c>
+      <c r="D42" s="63">
+        <v>143025</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="62">
+        <v>44233</v>
+      </c>
+      <c r="B43" s="63">
+        <v>46444</v>
+      </c>
+      <c r="C43" s="63">
+        <v>52805</v>
+      </c>
+      <c r="D43" s="63">
+        <v>99249</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="62">
+        <v>44234</v>
+      </c>
+      <c r="B44" s="63">
+        <v>28105</v>
+      </c>
+      <c r="C44" s="63">
+        <v>25433</v>
+      </c>
+      <c r="D44" s="63">
+        <v>53538</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="62">
+        <v>44235</v>
+      </c>
+      <c r="B45" s="63">
+        <v>53360</v>
+      </c>
+      <c r="C45" s="63">
+        <v>56630</v>
+      </c>
+      <c r="D45" s="63">
+        <v>109990</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="62">
+        <v>44236</v>
+      </c>
+      <c r="B46" s="63">
+        <v>59293</v>
+      </c>
+      <c r="C46" s="63">
+        <v>73230</v>
+      </c>
+      <c r="D46" s="63">
+        <v>132523</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="62">
+        <v>44237</v>
+      </c>
+      <c r="B47" s="63">
+        <v>73715</v>
+      </c>
+      <c r="C47" s="63">
+        <v>75144</v>
+      </c>
+      <c r="D47" s="63">
+        <v>148859</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="62">
+        <v>44238</v>
+      </c>
+      <c r="B48" s="63">
+        <v>73691</v>
+      </c>
+      <c r="C48" s="63">
+        <v>68210</v>
+      </c>
+      <c r="D48" s="63">
+        <v>141901</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="62">
+        <v>44239</v>
+      </c>
+      <c r="B49" s="63">
+        <v>80221</v>
+      </c>
+      <c r="C49" s="63">
+        <v>75845</v>
+      </c>
+      <c r="D49" s="63">
+        <v>156066</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="62">
+        <v>44240</v>
+      </c>
+      <c r="B50" s="63">
+        <v>61741</v>
+      </c>
+      <c r="C50" s="63">
+        <v>45983</v>
+      </c>
+      <c r="D50" s="63">
+        <v>107724</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="62">
+        <v>44241</v>
+      </c>
+      <c r="B51" s="63">
+        <v>39774</v>
+      </c>
+      <c r="C51" s="63">
+        <v>25017</v>
+      </c>
+      <c r="D51" s="63">
+        <v>64791</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="62">
+        <v>44242</v>
+      </c>
+      <c r="B52" s="63">
+        <v>70614</v>
+      </c>
+      <c r="C52" s="63">
+        <v>55815</v>
+      </c>
+      <c r="D52" s="63">
+        <v>126429</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="62">
+        <v>44243</v>
+      </c>
+      <c r="B53" s="63">
+        <v>81427</v>
+      </c>
+      <c r="C53" s="63">
+        <v>52945</v>
+      </c>
+      <c r="D53" s="63">
+        <v>134372</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="62">
+        <v>44244</v>
+      </c>
+      <c r="B54" s="63">
+        <v>94329</v>
+      </c>
+      <c r="C54" s="63">
+        <v>55394</v>
+      </c>
+      <c r="D54" s="63">
+        <v>149723</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="62">
+        <v>44245</v>
+      </c>
+      <c r="B55" s="63">
+        <v>91909</v>
+      </c>
+      <c r="C55" s="63">
+        <v>51673</v>
+      </c>
+      <c r="D55" s="63">
+        <v>143582</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="62">
+        <v>44246</v>
+      </c>
+      <c r="B56" s="63">
+        <v>98848</v>
+      </c>
+      <c r="C56" s="63">
+        <v>53668</v>
+      </c>
+      <c r="D56" s="63">
+        <v>152516</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="62">
+        <v>44247</v>
+      </c>
+      <c r="B57" s="63">
+        <v>76396</v>
+      </c>
+      <c r="C57" s="63">
+        <v>37726</v>
+      </c>
+      <c r="D57" s="63">
+        <v>114122</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="62">
+        <v>44248</v>
+      </c>
+      <c r="B58" s="63">
+        <v>56874</v>
+      </c>
+      <c r="C58" s="63">
+        <v>28891</v>
+      </c>
+      <c r="D58" s="63">
+        <v>85765</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="62">
+        <v>44249</v>
+      </c>
+      <c r="B59" s="63">
+        <v>99499</v>
+      </c>
+      <c r="C59" s="63">
+        <v>61060</v>
+      </c>
+      <c r="D59" s="63">
+        <v>160559</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="62">
+        <v>44250</v>
+      </c>
+      <c r="B60" s="63">
+        <v>106639</v>
+      </c>
+      <c r="C60" s="63">
+        <v>59883</v>
+      </c>
+      <c r="D60" s="63">
+        <v>166522</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="62">
+        <v>44251</v>
+      </c>
+      <c r="B61" s="63">
+        <v>115185</v>
+      </c>
+      <c r="C61" s="63">
+        <v>58832</v>
+      </c>
+      <c r="D61" s="63">
+        <v>174017</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="62">
+        <v>44252</v>
+      </c>
+      <c r="B62" s="63">
+        <v>129856</v>
+      </c>
+      <c r="C62" s="63">
+        <v>58352</v>
+      </c>
+      <c r="D62" s="63">
+        <v>188208</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="62">
+        <v>44253</v>
+      </c>
+      <c r="B63" s="63">
+        <v>143462</v>
+      </c>
+      <c r="C63" s="63">
+        <v>64220</v>
+      </c>
+      <c r="D63" s="63">
+        <v>207682</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="62">
+        <v>44254</v>
+      </c>
+      <c r="B64" s="63">
+        <v>108287</v>
+      </c>
+      <c r="C64" s="63">
+        <v>39902</v>
+      </c>
+      <c r="D64" s="63">
+        <v>148189</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="62">
+        <v>44255</v>
+      </c>
+      <c r="B65" s="63">
+        <v>83853</v>
+      </c>
+      <c r="C65" s="63">
+        <v>24236</v>
+      </c>
+      <c r="D65" s="63">
+        <v>108089</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="62">
+        <v>44256</v>
+      </c>
+      <c r="B66" s="63">
+        <v>145009</v>
+      </c>
+      <c r="C66" s="63">
+        <v>49327</v>
+      </c>
+      <c r="D66" s="63">
+        <v>194336</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="62">
+        <v>44257</v>
+      </c>
+      <c r="B67" s="63">
+        <v>164790</v>
+      </c>
+      <c r="C67" s="63">
+        <v>53614</v>
+      </c>
+      <c r="D67" s="63">
+        <v>218404</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="62">
+        <v>44258</v>
+      </c>
+      <c r="B68" s="63">
+        <v>173609</v>
+      </c>
+      <c r="C68" s="63">
+        <v>68108</v>
+      </c>
+      <c r="D68" s="63">
+        <v>241717</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="62">
+        <v>44259</v>
+      </c>
+      <c r="B69" s="63">
+        <v>178713</v>
+      </c>
+      <c r="C69" s="63">
+        <v>62692</v>
+      </c>
+      <c r="D69" s="63">
+        <v>241405</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="62">
+        <v>44260</v>
+      </c>
+      <c r="B70" s="63">
+        <v>199636</v>
+      </c>
+      <c r="C70" s="63">
+        <v>66527</v>
+      </c>
+      <c r="D70" s="63">
+        <v>266163</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="62">
+        <v>44261</v>
+      </c>
+      <c r="B71" s="63">
+        <v>152861</v>
+      </c>
+      <c r="C71" s="63">
+        <v>49141</v>
+      </c>
+      <c r="D71" s="63">
+        <v>202002</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="62">
+        <v>44262</v>
+      </c>
+      <c r="B72" s="63">
+        <v>114567</v>
+      </c>
+      <c r="C72" s="63">
+        <v>34641</v>
+      </c>
+      <c r="D72" s="63">
+        <v>149208</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="62">
+        <v>44263</v>
+      </c>
+      <c r="B73" s="63">
+        <v>185254</v>
+      </c>
+      <c r="C73" s="63">
+        <v>52508</v>
+      </c>
+      <c r="D73" s="63">
+        <v>237762</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="62">
+        <v>44264</v>
+      </c>
+      <c r="B74" s="63">
+        <v>195221</v>
+      </c>
+      <c r="C74" s="63">
+        <v>54773</v>
+      </c>
+      <c r="D74" s="63">
+        <v>249994</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="62">
+        <v>44265</v>
+      </c>
+      <c r="B75" s="63">
+        <v>217156</v>
+      </c>
+      <c r="C75" s="63">
+        <v>65482</v>
+      </c>
+      <c r="D75" s="63">
+        <v>282638</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="62">
+        <v>44266</v>
+      </c>
+      <c r="B76" s="63">
+        <v>219350</v>
+      </c>
+      <c r="C76" s="63">
+        <v>60900</v>
+      </c>
+      <c r="D76" s="63">
+        <v>280250</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="62">
+        <v>44267</v>
+      </c>
+      <c r="B77" s="63">
+        <v>249439</v>
+      </c>
+      <c r="C77" s="63">
+        <v>71458</v>
+      </c>
+      <c r="D77" s="63">
+        <v>320897</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="62">
+        <v>44268</v>
+      </c>
+      <c r="B78" s="63">
+        <v>196306</v>
+      </c>
+      <c r="C78" s="63">
+        <v>49375</v>
+      </c>
+      <c r="D78" s="63">
+        <v>245681</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="62">
+        <v>44269</v>
+      </c>
+      <c r="B79" s="63">
+        <v>134812</v>
+      </c>
+      <c r="C79" s="63">
+        <v>36026</v>
+      </c>
+      <c r="D79" s="63">
+        <v>170838</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="62">
+        <v>44270</v>
+      </c>
+      <c r="B80" s="63">
+        <v>188825</v>
+      </c>
+      <c r="C80" s="63">
+        <v>58822</v>
+      </c>
+      <c r="D80" s="63">
+        <v>247647</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="62">
+        <v>44271</v>
+      </c>
+      <c r="B81" s="63">
+        <v>113341</v>
+      </c>
+      <c r="C81" s="63">
+        <v>67002</v>
+      </c>
+      <c r="D81" s="63">
+        <v>180343</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="62">
+        <v>44272</v>
+      </c>
+      <c r="B82" s="63">
+        <v>124937</v>
+      </c>
+      <c r="C82" s="63">
+        <v>78884</v>
+      </c>
+      <c r="D82" s="63">
+        <v>203821</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="62">
+        <v>44273</v>
+      </c>
+      <c r="B83" s="63">
+        <v>119107</v>
+      </c>
+      <c r="C83" s="63">
+        <v>74783</v>
+      </c>
+      <c r="D83" s="63">
+        <v>193890</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="62">
+        <v>44274</v>
+      </c>
+      <c r="B84" s="63">
+        <v>158860</v>
+      </c>
+      <c r="C84" s="63">
+        <v>82103</v>
+      </c>
+      <c r="D84" s="63">
+        <v>240963</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="62">
+        <v>44275</v>
+      </c>
+      <c r="B85" s="63">
+        <v>164531</v>
+      </c>
+      <c r="C85" s="63">
+        <v>53842</v>
+      </c>
+      <c r="D85" s="63">
+        <v>218373</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="62">
+        <v>44276</v>
+      </c>
+      <c r="B86" s="63">
+        <v>126728</v>
+      </c>
+      <c r="C86" s="63">
+        <v>38760</v>
+      </c>
+      <c r="D86" s="63">
+        <v>165488</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="62">
+        <v>44277</v>
+      </c>
+      <c r="B87" s="63">
+        <v>188665</v>
+      </c>
+      <c r="C87" s="63">
+        <v>76219</v>
+      </c>
+      <c r="D87" s="63">
+        <v>264884</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="62">
+        <v>44278</v>
+      </c>
+      <c r="B88" s="63">
+        <v>213271</v>
+      </c>
+      <c r="C88" s="63">
+        <v>83554</v>
+      </c>
+      <c r="D88" s="63">
+        <v>296825</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="62">
+        <v>44279</v>
+      </c>
+      <c r="B89" s="63">
+        <v>243072</v>
+      </c>
+      <c r="C89" s="63">
+        <v>87758</v>
+      </c>
+      <c r="D89" s="63">
+        <v>330830</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="62">
+        <v>44280</v>
+      </c>
+      <c r="B90" s="63">
+        <v>253353</v>
+      </c>
+      <c r="C90" s="63">
+        <v>79448</v>
+      </c>
+      <c r="D90" s="63">
+        <v>332801</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="62">
+        <v>44281</v>
+      </c>
+      <c r="B91" s="63">
+        <v>280118</v>
+      </c>
+      <c r="C91" s="63">
+        <v>88624</v>
+      </c>
+      <c r="D91" s="63">
+        <v>368742</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="62">
+        <v>44282</v>
+      </c>
+      <c r="B92" s="63">
+        <v>220592</v>
+      </c>
+      <c r="C92" s="63">
+        <v>63208</v>
+      </c>
+      <c r="D92" s="63">
+        <v>283800</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="62">
+        <v>44283</v>
+      </c>
+      <c r="B93" s="63">
+        <v>142279</v>
+      </c>
+      <c r="C93" s="63">
+        <v>52752</v>
+      </c>
+      <c r="D93" s="63">
+        <v>195031</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="62">
+        <v>44284</v>
+      </c>
+      <c r="B94" s="63">
+        <v>217234</v>
+      </c>
+      <c r="C94" s="63">
+        <v>88523</v>
+      </c>
+      <c r="D94" s="63">
+        <v>305757</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="62">
+        <v>44285</v>
+      </c>
+      <c r="B95" s="63">
+        <v>231049</v>
+      </c>
+      <c r="C95" s="63">
+        <v>92647</v>
+      </c>
+      <c r="D95" s="63">
+        <v>323696</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="62">
+        <v>44286</v>
+      </c>
+      <c r="B96" s="63">
+        <v>232992</v>
+      </c>
+      <c r="C96" s="63">
+        <v>102394</v>
+      </c>
+      <c r="D96" s="63">
+        <v>335386</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="62">
+        <v>44287</v>
+      </c>
+      <c r="B97" s="63">
+        <v>226040</v>
+      </c>
+      <c r="C97" s="63">
+        <v>91621</v>
+      </c>
+      <c r="D97" s="63">
+        <v>317661</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="62">
+        <v>44288</v>
+      </c>
+      <c r="B98" s="63">
+        <v>156864</v>
+      </c>
+      <c r="C98" s="63">
+        <v>71401</v>
+      </c>
+      <c r="D98" s="63">
+        <v>228265</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="62">
+        <v>44289</v>
+      </c>
+      <c r="B99" s="63">
+        <v>163058</v>
+      </c>
+      <c r="C99" s="63">
+        <v>66044</v>
+      </c>
+      <c r="D99" s="63">
+        <v>229102</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="62">
+        <v>44290</v>
+      </c>
+      <c r="B100" s="63">
+        <v>141353</v>
+      </c>
+      <c r="C100" s="63">
+        <v>53528</v>
+      </c>
+      <c r="D100" s="63">
+        <v>194881</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="62">
+        <v>44291</v>
+      </c>
+      <c r="B101" s="63">
+        <v>175942</v>
+      </c>
+      <c r="C101" s="63">
+        <v>73329</v>
+      </c>
+      <c r="D101" s="63">
+        <v>249271</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="62">
+        <v>44292</v>
+      </c>
+      <c r="B102" s="63">
+        <v>277210</v>
+      </c>
+      <c r="C102" s="63">
+        <v>98377</v>
+      </c>
+      <c r="D102" s="63">
+        <v>375587</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="62">
+        <v>44293</v>
+      </c>
+      <c r="B103" s="63">
+        <v>576288</v>
+      </c>
+      <c r="C103" s="63">
+        <v>95249</v>
+      </c>
+      <c r="D103" s="63">
+        <v>671537</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="62">
+        <v>44294</v>
+      </c>
+      <c r="B104" s="63">
+        <v>636315</v>
+      </c>
+      <c r="C104" s="63">
+        <v>88265</v>
+      </c>
+      <c r="D104" s="63">
+        <v>724580</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="62">
+        <v>44295</v>
+      </c>
+      <c r="B105" s="63">
+        <v>529682</v>
+      </c>
+      <c r="C105" s="63">
+        <v>85431</v>
+      </c>
+      <c r="D105" s="63">
+        <v>615113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="62">
+        <v>44296</v>
+      </c>
+      <c r="B106" s="63">
+        <v>296631</v>
+      </c>
+      <c r="C106" s="63">
+        <v>64391</v>
+      </c>
+      <c r="D106" s="63">
+        <v>361022</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="62">
+        <v>44297</v>
+      </c>
+      <c r="B107" s="63">
+        <v>205724</v>
+      </c>
+      <c r="C107" s="63">
+        <v>49618</v>
+      </c>
+      <c r="D107" s="63">
+        <v>255342</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="62">
+        <v>44298</v>
+      </c>
+      <c r="B108" s="63">
+        <v>332569</v>
+      </c>
+      <c r="C108" s="63">
+        <v>74382</v>
+      </c>
+      <c r="D108" s="63">
+        <v>406951</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="62">
+        <v>44299</v>
+      </c>
+      <c r="B109" s="63">
+        <v>464701</v>
+      </c>
+      <c r="C109" s="63">
+        <v>65836</v>
+      </c>
+      <c r="D109" s="63">
+        <v>530537</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="64"/>
+      <c r="B110" s="64"/>
+      <c r="C110" s="64"/>
+      <c r="D110" s="64"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="65" t="s">
+        <v>19</v>
+      </c>
+      <c r="B111" s="66">
+        <v>14058329</v>
+      </c>
+      <c r="C111" s="66">
+        <v>5186135</v>
+      </c>
+      <c r="D111" s="66">
+        <v>19244464</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="64"/>
+      <c r="B112" s="64"/>
+      <c r="C112" s="64"/>
+      <c r="D112" s="64"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="64" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="80">
-        <v>44192</v>
-      </c>
-      <c r="B2" s="81">
-        <v>24159</v>
-      </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81">
-        <v>24159</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="80">
-        <v>44193</v>
-      </c>
-      <c r="B3" s="81">
-        <v>18383</v>
-      </c>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81">
-        <v>18383</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="80">
-        <v>44194</v>
-      </c>
-      <c r="B4" s="81">
-        <v>48305</v>
-      </c>
-      <c r="C4" s="81"/>
-      <c r="D4" s="81">
-        <v>48305</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="80">
-        <v>44195</v>
-      </c>
-      <c r="B5" s="81">
-        <v>61542</v>
-      </c>
-      <c r="C5" s="81"/>
-      <c r="D5" s="81">
-        <v>61542</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="80">
-        <v>44196</v>
-      </c>
-      <c r="B6" s="81">
-        <v>49555</v>
-      </c>
-      <c r="C6" s="81"/>
-      <c r="D6" s="81">
-        <v>49555</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="80">
-        <v>44197</v>
-      </c>
-      <c r="B7" s="81">
-        <v>19271</v>
-      </c>
-      <c r="C7" s="81"/>
-      <c r="D7" s="81">
-        <v>19271</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="80">
-        <v>44198</v>
-      </c>
-      <c r="B8" s="81">
-        <v>52442</v>
-      </c>
-      <c r="C8" s="81"/>
-      <c r="D8" s="81">
-        <v>52442</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="80">
-        <v>44199</v>
-      </c>
-      <c r="B9" s="81">
-        <v>24148</v>
-      </c>
-      <c r="C9" s="81"/>
-      <c r="D9" s="81">
-        <v>24148</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="80">
-        <v>44200</v>
-      </c>
-      <c r="B10" s="81">
-        <v>48306</v>
-      </c>
-      <c r="C10" s="81"/>
-      <c r="D10" s="81">
-        <v>48306</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="80">
-        <v>44201</v>
-      </c>
-      <c r="B11" s="81">
-        <v>53341</v>
-      </c>
-      <c r="C11" s="81"/>
-      <c r="D11" s="81">
-        <v>53341</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="80">
-        <v>44202</v>
-      </c>
-      <c r="B12" s="81">
-        <v>62995</v>
-      </c>
-      <c r="C12" s="81"/>
-      <c r="D12" s="81">
-        <v>62995</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="80">
-        <v>44203</v>
-      </c>
-      <c r="B13" s="81">
-        <v>56201</v>
-      </c>
-      <c r="C13" s="81"/>
-      <c r="D13" s="81">
-        <v>56201</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="80">
-        <v>44204</v>
-      </c>
-      <c r="B14" s="81">
-        <v>63101</v>
-      </c>
-      <c r="C14" s="81"/>
-      <c r="D14" s="81">
-        <v>63101</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="80">
-        <v>44205</v>
-      </c>
-      <c r="B15" s="81">
-        <v>61176</v>
-      </c>
-      <c r="C15" s="81"/>
-      <c r="D15" s="81">
-        <v>61176</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="80">
-        <v>44206</v>
-      </c>
-      <c r="B16" s="81">
-        <v>35132</v>
-      </c>
-      <c r="C16" s="81"/>
-      <c r="D16" s="81">
-        <v>35132</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="80">
-        <v>44207</v>
-      </c>
-      <c r="B17" s="81">
-        <v>66389</v>
-      </c>
-      <c r="C17" s="81"/>
-      <c r="D17" s="81">
-        <v>66389</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="80">
-        <v>44208</v>
-      </c>
-      <c r="B18" s="81">
-        <v>82874</v>
-      </c>
-      <c r="C18" s="81"/>
-      <c r="D18" s="81">
-        <v>82874</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="80">
-        <v>44209</v>
-      </c>
-      <c r="B19" s="81">
-        <v>111147</v>
-      </c>
-      <c r="C19" s="81"/>
-      <c r="D19" s="81">
-        <v>111147</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="80">
-        <v>44210</v>
-      </c>
-      <c r="B20" s="81">
-        <v>82836</v>
-      </c>
-      <c r="C20" s="81"/>
-      <c r="D20" s="81">
-        <v>82836</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="80">
-        <v>44211</v>
-      </c>
-      <c r="B21" s="81">
-        <v>89715</v>
-      </c>
-      <c r="C21" s="81">
-        <v>712</v>
-      </c>
-      <c r="D21" s="81">
-        <v>90427</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="80">
-        <v>44212</v>
-      </c>
-      <c r="B22" s="81">
-        <v>56317</v>
-      </c>
-      <c r="C22" s="81">
-        <v>1036</v>
-      </c>
-      <c r="D22" s="81">
-        <v>57353</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="80">
-        <v>44213</v>
-      </c>
-      <c r="B23" s="81">
-        <v>30827</v>
-      </c>
-      <c r="C23" s="81">
-        <v>16667</v>
-      </c>
-      <c r="D23" s="81">
-        <v>47494</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="80">
-        <v>44214</v>
-      </c>
-      <c r="B24" s="81">
-        <v>66053</v>
-      </c>
-      <c r="C24" s="81">
-        <v>15745</v>
-      </c>
-      <c r="D24" s="81">
-        <v>81798</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="80">
-        <v>44215</v>
-      </c>
-      <c r="B25" s="81">
-        <v>81041</v>
-      </c>
-      <c r="C25" s="81">
-        <v>32452</v>
-      </c>
-      <c r="D25" s="81">
-        <v>113493</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="80">
-        <v>44216</v>
-      </c>
-      <c r="B26" s="81">
-        <v>80333</v>
-      </c>
-      <c r="C26" s="81">
-        <v>51055</v>
-      </c>
-      <c r="D26" s="81">
-        <v>131388</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="80">
-        <v>44217</v>
-      </c>
-      <c r="B27" s="81">
-        <v>64349</v>
-      </c>
-      <c r="C27" s="81">
-        <v>39674</v>
-      </c>
-      <c r="D27" s="81">
-        <v>104023</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="80">
-        <v>44218</v>
-      </c>
-      <c r="B28" s="81">
-        <v>67515</v>
-      </c>
-      <c r="C28" s="81">
-        <v>34378</v>
-      </c>
-      <c r="D28" s="81">
-        <v>101893</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="80">
-        <v>44219</v>
-      </c>
-      <c r="B29" s="81">
-        <v>40686</v>
-      </c>
-      <c r="C29" s="81">
-        <v>44677</v>
-      </c>
-      <c r="D29" s="81">
-        <v>85363</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="80">
-        <v>44220</v>
-      </c>
-      <c r="B30" s="81">
-        <v>25596</v>
-      </c>
-      <c r="C30" s="81">
-        <v>23897</v>
-      </c>
-      <c r="D30" s="81">
-        <v>49493</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="80">
-        <v>44221</v>
-      </c>
-      <c r="B31" s="81">
-        <v>58179</v>
-      </c>
-      <c r="C31" s="81">
-        <v>37792</v>
-      </c>
-      <c r="D31" s="81">
-        <v>95971</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="80">
-        <v>44222</v>
-      </c>
-      <c r="B32" s="81">
-        <v>50966</v>
-      </c>
-      <c r="C32" s="81">
-        <v>48453</v>
-      </c>
-      <c r="D32" s="81">
-        <v>99419</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="80">
-        <v>44223</v>
-      </c>
-      <c r="B33" s="81">
-        <v>51577</v>
-      </c>
-      <c r="C33" s="81">
-        <v>59331</v>
-      </c>
-      <c r="D33" s="81">
-        <v>110908</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="80">
-        <v>44224</v>
-      </c>
-      <c r="B34" s="81">
-        <v>45185</v>
-      </c>
-      <c r="C34" s="81">
-        <v>46146</v>
-      </c>
-      <c r="D34" s="81">
-        <v>91331</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="80">
-        <v>44225</v>
-      </c>
-      <c r="B35" s="81">
-        <v>51179</v>
-      </c>
-      <c r="C35" s="81">
-        <v>57339</v>
-      </c>
-      <c r="D35" s="81">
-        <v>108518</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="80">
-        <v>44226</v>
-      </c>
-      <c r="B36" s="81">
-        <v>35290</v>
-      </c>
-      <c r="C36" s="81">
-        <v>51306</v>
-      </c>
-      <c r="D36" s="81">
-        <v>86596</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="80">
-        <v>44227</v>
-      </c>
-      <c r="B37" s="81">
-        <v>26718</v>
-      </c>
-      <c r="C37" s="81">
-        <v>31051</v>
-      </c>
-      <c r="D37" s="81">
-        <v>57769</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="80">
-        <v>44228</v>
-      </c>
-      <c r="B38" s="81">
-        <v>59267</v>
-      </c>
-      <c r="C38" s="81">
-        <v>62136</v>
-      </c>
-      <c r="D38" s="81">
-        <v>121403</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="80">
-        <v>44229</v>
-      </c>
-      <c r="B39" s="81">
-        <v>63543</v>
-      </c>
-      <c r="C39" s="81">
-        <v>66948</v>
-      </c>
-      <c r="D39" s="81">
-        <v>130491</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="80">
-        <v>44230</v>
-      </c>
-      <c r="B40" s="81">
-        <v>63689</v>
-      </c>
-      <c r="C40" s="81">
-        <v>94243</v>
-      </c>
-      <c r="D40" s="81">
-        <v>157932</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="80">
-        <v>44231</v>
-      </c>
-      <c r="B41" s="81">
-        <v>61020</v>
-      </c>
-      <c r="C41" s="81">
-        <v>70133</v>
-      </c>
-      <c r="D41" s="81">
-        <v>131153</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="80">
-        <v>44232</v>
-      </c>
-      <c r="B42" s="81">
-        <v>66405</v>
-      </c>
-      <c r="C42" s="81">
-        <v>76620</v>
-      </c>
-      <c r="D42" s="81">
-        <v>143025</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="80">
-        <v>44233</v>
-      </c>
-      <c r="B43" s="81">
-        <v>46444</v>
-      </c>
-      <c r="C43" s="81">
-        <v>52805</v>
-      </c>
-      <c r="D43" s="81">
-        <v>99249</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="80">
-        <v>44234</v>
-      </c>
-      <c r="B44" s="81">
-        <v>28105</v>
-      </c>
-      <c r="C44" s="81">
-        <v>25433</v>
-      </c>
-      <c r="D44" s="81">
-        <v>53538</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="80">
-        <v>44235</v>
-      </c>
-      <c r="B45" s="81">
-        <v>53360</v>
-      </c>
-      <c r="C45" s="81">
-        <v>56630</v>
-      </c>
-      <c r="D45" s="81">
-        <v>109990</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="80">
-        <v>44236</v>
-      </c>
-      <c r="B46" s="81">
-        <v>59293</v>
-      </c>
-      <c r="C46" s="81">
-        <v>73230</v>
-      </c>
-      <c r="D46" s="81">
-        <v>132523</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="80">
-        <v>44237</v>
-      </c>
-      <c r="B47" s="81">
-        <v>73715</v>
-      </c>
-      <c r="C47" s="81">
-        <v>75144</v>
-      </c>
-      <c r="D47" s="81">
-        <v>148859</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="80">
-        <v>44238</v>
-      </c>
-      <c r="B48" s="81">
-        <v>73691</v>
-      </c>
-      <c r="C48" s="81">
-        <v>68210</v>
-      </c>
-      <c r="D48" s="81">
-        <v>141901</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="80">
-        <v>44239</v>
-      </c>
-      <c r="B49" s="81">
-        <v>80221</v>
-      </c>
-      <c r="C49" s="81">
-        <v>75845</v>
-      </c>
-      <c r="D49" s="81">
-        <v>156066</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="80">
-        <v>44240</v>
-      </c>
-      <c r="B50" s="81">
-        <v>61741</v>
-      </c>
-      <c r="C50" s="81">
-        <v>45983</v>
-      </c>
-      <c r="D50" s="81">
-        <v>107724</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="80">
-        <v>44241</v>
-      </c>
-      <c r="B51" s="81">
-        <v>39774</v>
-      </c>
-      <c r="C51" s="81">
-        <v>25017</v>
-      </c>
-      <c r="D51" s="81">
-        <v>64791</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="80">
-        <v>44242</v>
-      </c>
-      <c r="B52" s="81">
-        <v>70614</v>
-      </c>
-      <c r="C52" s="81">
-        <v>55815</v>
-      </c>
-      <c r="D52" s="81">
-        <v>126429</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="80">
-        <v>44243</v>
-      </c>
-      <c r="B53" s="81">
-        <v>81427</v>
-      </c>
-      <c r="C53" s="81">
-        <v>52945</v>
-      </c>
-      <c r="D53" s="81">
-        <v>134372</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="80">
-        <v>44244</v>
-      </c>
-      <c r="B54" s="81">
-        <v>94329</v>
-      </c>
-      <c r="C54" s="81">
-        <v>55394</v>
-      </c>
-      <c r="D54" s="81">
-        <v>149723</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="80">
-        <v>44245</v>
-      </c>
-      <c r="B55" s="81">
-        <v>91909</v>
-      </c>
-      <c r="C55" s="81">
-        <v>51673</v>
-      </c>
-      <c r="D55" s="81">
-        <v>143582</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="80">
-        <v>44246</v>
-      </c>
-      <c r="B56" s="81">
-        <v>98848</v>
-      </c>
-      <c r="C56" s="81">
-        <v>53668</v>
-      </c>
-      <c r="D56" s="81">
-        <v>152516</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="80">
-        <v>44247</v>
-      </c>
-      <c r="B57" s="81">
-        <v>76396</v>
-      </c>
-      <c r="C57" s="81">
-        <v>37726</v>
-      </c>
-      <c r="D57" s="81">
-        <v>114122</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="80">
-        <v>44248</v>
-      </c>
-      <c r="B58" s="81">
-        <v>56874</v>
-      </c>
-      <c r="C58" s="81">
-        <v>28891</v>
-      </c>
-      <c r="D58" s="81">
-        <v>85765</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="80">
-        <v>44249</v>
-      </c>
-      <c r="B59" s="81">
-        <v>99499</v>
-      </c>
-      <c r="C59" s="81">
-        <v>61060</v>
-      </c>
-      <c r="D59" s="81">
-        <v>160559</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="80">
-        <v>44250</v>
-      </c>
-      <c r="B60" s="81">
-        <v>106639</v>
-      </c>
-      <c r="C60" s="81">
-        <v>59883</v>
-      </c>
-      <c r="D60" s="81">
-        <v>166522</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="80">
-        <v>44251</v>
-      </c>
-      <c r="B61" s="81">
-        <v>115185</v>
-      </c>
-      <c r="C61" s="81">
-        <v>58832</v>
-      </c>
-      <c r="D61" s="81">
-        <v>174017</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="80">
-        <v>44252</v>
-      </c>
-      <c r="B62" s="81">
-        <v>129856</v>
-      </c>
-      <c r="C62" s="81">
-        <v>58352</v>
-      </c>
-      <c r="D62" s="81">
-        <v>188208</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="80">
-        <v>44253</v>
-      </c>
-      <c r="B63" s="81">
-        <v>143462</v>
-      </c>
-      <c r="C63" s="81">
-        <v>64220</v>
-      </c>
-      <c r="D63" s="81">
-        <v>207682</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="80">
-        <v>44254</v>
-      </c>
-      <c r="B64" s="81">
-        <v>108287</v>
-      </c>
-      <c r="C64" s="81">
-        <v>39902</v>
-      </c>
-      <c r="D64" s="81">
-        <v>148189</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="80">
-        <v>44255</v>
-      </c>
-      <c r="B65" s="81">
-        <v>83853</v>
-      </c>
-      <c r="C65" s="81">
-        <v>24236</v>
-      </c>
-      <c r="D65" s="81">
-        <v>108089</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="80">
-        <v>44256</v>
-      </c>
-      <c r="B66" s="81">
-        <v>145009</v>
-      </c>
-      <c r="C66" s="81">
-        <v>49327</v>
-      </c>
-      <c r="D66" s="81">
-        <v>194336</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="80">
-        <v>44257</v>
-      </c>
-      <c r="B67" s="81">
-        <v>164790</v>
-      </c>
-      <c r="C67" s="81">
-        <v>53614</v>
-      </c>
-      <c r="D67" s="81">
-        <v>218404</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="80">
-        <v>44258</v>
-      </c>
-      <c r="B68" s="81">
-        <v>173609</v>
-      </c>
-      <c r="C68" s="81">
-        <v>68108</v>
-      </c>
-      <c r="D68" s="81">
-        <v>241717</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="80">
-        <v>44259</v>
-      </c>
-      <c r="B69" s="81">
-        <v>178713</v>
-      </c>
-      <c r="C69" s="81">
-        <v>62692</v>
-      </c>
-      <c r="D69" s="81">
-        <v>241405</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="80">
-        <v>44260</v>
-      </c>
-      <c r="B70" s="81">
-        <v>199636</v>
-      </c>
-      <c r="C70" s="81">
-        <v>66527</v>
-      </c>
-      <c r="D70" s="81">
-        <v>266163</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="80">
-        <v>44261</v>
-      </c>
-      <c r="B71" s="81">
-        <v>152861</v>
-      </c>
-      <c r="C71" s="81">
-        <v>49141</v>
-      </c>
-      <c r="D71" s="81">
-        <v>202002</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="80">
-        <v>44262</v>
-      </c>
-      <c r="B72" s="81">
-        <v>114567</v>
-      </c>
-      <c r="C72" s="81">
-        <v>34641</v>
-      </c>
-      <c r="D72" s="81">
-        <v>149208</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="80">
-        <v>44263</v>
-      </c>
-      <c r="B73" s="81">
-        <v>185254</v>
-      </c>
-      <c r="C73" s="81">
-        <v>52508</v>
-      </c>
-      <c r="D73" s="81">
-        <v>237762</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="80">
-        <v>44264</v>
-      </c>
-      <c r="B74" s="81">
-        <v>195221</v>
-      </c>
-      <c r="C74" s="81">
-        <v>54773</v>
-      </c>
-      <c r="D74" s="81">
-        <v>249994</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="80">
-        <v>44265</v>
-      </c>
-      <c r="B75" s="81">
-        <v>217156</v>
-      </c>
-      <c r="C75" s="81">
-        <v>65482</v>
-      </c>
-      <c r="D75" s="81">
-        <v>282638</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="80">
-        <v>44266</v>
-      </c>
-      <c r="B76" s="81">
-        <v>219350</v>
-      </c>
-      <c r="C76" s="81">
-        <v>60900</v>
-      </c>
-      <c r="D76" s="81">
-        <v>280250</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="80">
-        <v>44267</v>
-      </c>
-      <c r="B77" s="81">
-        <v>249439</v>
-      </c>
-      <c r="C77" s="81">
-        <v>71458</v>
-      </c>
-      <c r="D77" s="81">
-        <v>320897</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="80">
-        <v>44268</v>
-      </c>
-      <c r="B78" s="81">
-        <v>196306</v>
-      </c>
-      <c r="C78" s="81">
-        <v>49375</v>
-      </c>
-      <c r="D78" s="81">
-        <v>245681</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="80">
-        <v>44269</v>
-      </c>
-      <c r="B79" s="81">
-        <v>134812</v>
-      </c>
-      <c r="C79" s="81">
-        <v>36026</v>
-      </c>
-      <c r="D79" s="81">
-        <v>170838</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="80">
-        <v>44270</v>
-      </c>
-      <c r="B80" s="81">
-        <v>188825</v>
-      </c>
-      <c r="C80" s="81">
-        <v>58822</v>
-      </c>
-      <c r="D80" s="81">
-        <v>247647</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="80">
-        <v>44271</v>
-      </c>
-      <c r="B81" s="81">
-        <v>113341</v>
-      </c>
-      <c r="C81" s="81">
-        <v>67002</v>
-      </c>
-      <c r="D81" s="81">
-        <v>180343</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="80">
-        <v>44272</v>
-      </c>
-      <c r="B82" s="81">
-        <v>124937</v>
-      </c>
-      <c r="C82" s="81">
-        <v>78884</v>
-      </c>
-      <c r="D82" s="81">
-        <v>203821</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="80">
-        <v>44273</v>
-      </c>
-      <c r="B83" s="81">
-        <v>119107</v>
-      </c>
-      <c r="C83" s="81">
-        <v>74783</v>
-      </c>
-      <c r="D83" s="81">
-        <v>193890</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="80">
-        <v>44274</v>
-      </c>
-      <c r="B84" s="81">
-        <v>158860</v>
-      </c>
-      <c r="C84" s="81">
-        <v>82103</v>
-      </c>
-      <c r="D84" s="81">
-        <v>240963</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="80">
-        <v>44275</v>
-      </c>
-      <c r="B85" s="81">
-        <v>164531</v>
-      </c>
-      <c r="C85" s="81">
-        <v>53842</v>
-      </c>
-      <c r="D85" s="81">
-        <v>218373</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="80">
-        <v>44276</v>
-      </c>
-      <c r="B86" s="81">
-        <v>126728</v>
-      </c>
-      <c r="C86" s="81">
-        <v>38760</v>
-      </c>
-      <c r="D86" s="81">
-        <v>165488</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="80">
-        <v>44277</v>
-      </c>
-      <c r="B87" s="81">
-        <v>188665</v>
-      </c>
-      <c r="C87" s="81">
-        <v>76219</v>
-      </c>
-      <c r="D87" s="81">
-        <v>264884</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="80">
-        <v>44278</v>
-      </c>
-      <c r="B88" s="81">
-        <v>213271</v>
-      </c>
-      <c r="C88" s="81">
-        <v>83554</v>
-      </c>
-      <c r="D88" s="81">
-        <v>296825</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="80">
-        <v>44279</v>
-      </c>
-      <c r="B89" s="81">
-        <v>243072</v>
-      </c>
-      <c r="C89" s="81">
-        <v>87758</v>
-      </c>
-      <c r="D89" s="81">
-        <v>330830</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="80">
-        <v>44280</v>
-      </c>
-      <c r="B90" s="81">
-        <v>253353</v>
-      </c>
-      <c r="C90" s="81">
-        <v>79448</v>
-      </c>
-      <c r="D90" s="81">
-        <v>332801</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="80">
-        <v>44281</v>
-      </c>
-      <c r="B91" s="81">
-        <v>280118</v>
-      </c>
-      <c r="C91" s="81">
-        <v>88624</v>
-      </c>
-      <c r="D91" s="81">
-        <v>368742</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="80">
-        <v>44282</v>
-      </c>
-      <c r="B92" s="81">
-        <v>220592</v>
-      </c>
-      <c r="C92" s="81">
-        <v>63208</v>
-      </c>
-      <c r="D92" s="81">
-        <v>283800</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="80">
-        <v>44283</v>
-      </c>
-      <c r="B93" s="81">
-        <v>142279</v>
-      </c>
-      <c r="C93" s="81">
-        <v>52752</v>
-      </c>
-      <c r="D93" s="81">
-        <v>195031</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="80">
-        <v>44284</v>
-      </c>
-      <c r="B94" s="81">
-        <v>217234</v>
-      </c>
-      <c r="C94" s="81">
-        <v>88523</v>
-      </c>
-      <c r="D94" s="81">
-        <v>305757</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="80">
-        <v>44285</v>
-      </c>
-      <c r="B95" s="81">
-        <v>231049</v>
-      </c>
-      <c r="C95" s="81">
-        <v>92647</v>
-      </c>
-      <c r="D95" s="81">
-        <v>323696</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="80">
-        <v>44286</v>
-      </c>
-      <c r="B96" s="81">
-        <v>232992</v>
-      </c>
-      <c r="C96" s="81">
-        <v>102394</v>
-      </c>
-      <c r="D96" s="81">
-        <v>335386</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="80">
-        <v>44287</v>
-      </c>
-      <c r="B97" s="81">
-        <v>226040</v>
-      </c>
-      <c r="C97" s="81">
-        <v>91621</v>
-      </c>
-      <c r="D97" s="81">
-        <v>317661</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="80">
-        <v>44288</v>
-      </c>
-      <c r="B98" s="81">
-        <v>156864</v>
-      </c>
-      <c r="C98" s="81">
-        <v>71401</v>
-      </c>
-      <c r="D98" s="81">
-        <v>228265</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="80">
-        <v>44289</v>
-      </c>
-      <c r="B99" s="81">
-        <v>163058</v>
-      </c>
-      <c r="C99" s="81">
-        <v>66044</v>
-      </c>
-      <c r="D99" s="81">
-        <v>229102</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="80">
-        <v>44290</v>
-      </c>
-      <c r="B100" s="81">
-        <v>141353</v>
-      </c>
-      <c r="C100" s="81">
-        <v>53528</v>
-      </c>
-      <c r="D100" s="81">
-        <v>194881</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="80">
-        <v>44291</v>
-      </c>
-      <c r="B101" s="81">
-        <v>175942</v>
-      </c>
-      <c r="C101" s="81">
-        <v>73329</v>
-      </c>
-      <c r="D101" s="81">
-        <v>249271</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="80">
-        <v>44292</v>
-      </c>
-      <c r="B102" s="81">
-        <v>277210</v>
-      </c>
-      <c r="C102" s="81">
-        <v>98377</v>
-      </c>
-      <c r="D102" s="81">
-        <v>375587</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="80">
-        <v>44293</v>
-      </c>
-      <c r="B103" s="81">
-        <v>576288</v>
-      </c>
-      <c r="C103" s="81">
-        <v>95249</v>
-      </c>
-      <c r="D103" s="81">
-        <v>671537</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="80">
-        <v>44294</v>
-      </c>
-      <c r="B104" s="81">
-        <v>636315</v>
-      </c>
-      <c r="C104" s="81">
-        <v>88265</v>
-      </c>
-      <c r="D104" s="81">
-        <v>724580</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="80">
-        <v>44295</v>
-      </c>
-      <c r="B105" s="81">
-        <v>529682</v>
-      </c>
-      <c r="C105" s="81">
-        <v>85431</v>
-      </c>
-      <c r="D105" s="81">
-        <v>615113</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="80">
-        <v>44296</v>
-      </c>
-      <c r="B106" s="81">
-        <v>296631</v>
-      </c>
-      <c r="C106" s="81">
-        <v>64391</v>
-      </c>
-      <c r="D106" s="81">
-        <v>361022</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="80">
-        <v>44297</v>
-      </c>
-      <c r="B107" s="81">
-        <v>205724</v>
-      </c>
-      <c r="C107" s="81">
-        <v>49618</v>
-      </c>
-      <c r="D107" s="81">
-        <v>255342</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="80">
-        <v>44298</v>
-      </c>
-      <c r="B108" s="81">
-        <v>332569</v>
-      </c>
-      <c r="C108" s="81">
-        <v>74382</v>
-      </c>
-      <c r="D108" s="81">
-        <v>406951</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="80">
-        <v>44299</v>
-      </c>
-      <c r="B109" s="81">
-        <v>464701</v>
-      </c>
-      <c r="C109" s="81">
-        <v>65836</v>
-      </c>
-      <c r="D109" s="81">
-        <v>530537</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="82"/>
-      <c r="B110" s="82"/>
-      <c r="C110" s="82"/>
-      <c r="D110" s="82"/>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="83" t="s">
-        <v>19</v>
-      </c>
-      <c r="B111" s="84">
-        <v>14058329</v>
-      </c>
-      <c r="C111" s="84">
-        <v>5186135</v>
-      </c>
-      <c r="D111" s="84">
-        <v>19244464</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="82"/>
-      <c r="B112" s="82"/>
-      <c r="C112" s="82"/>
-      <c r="D112" s="82"/>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="82" t="s">
-        <v>77</v>
-      </c>
-      <c r="B113" s="82"/>
-      <c r="C113" s="82"/>
-      <c r="D113" s="82"/>
+      <c r="B113" s="64"/>
+      <c r="C113" s="64"/>
+      <c r="D113" s="64"/>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A114" s="82"/>
-      <c r="B114" s="82"/>
-      <c r="C114" s="82"/>
-      <c r="D114" s="82"/>
+      <c r="A114" s="64"/>
+      <c r="B114" s="64"/>
+      <c r="C114" s="64"/>
+      <c r="D114" s="64"/>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115" s="82"/>
-      <c r="B115" s="82"/>
-      <c r="C115" s="82"/>
-      <c r="D115" s="82"/>
+      <c r="A115" s="64"/>
+      <c r="B115" s="64"/>
+      <c r="C115" s="64"/>
+      <c r="D115" s="64"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
